--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128752933</v>
       </c>
       <c r="B2" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128754036</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 40437-2025 artfynd.xlsx
+++ b/artfynd/A 40437-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128752933</v>
+        <v>128754036</v>
       </c>
       <c r="B2" t="n">
-        <v>97549</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -714,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347987</v>
+        <v>348109</v>
       </c>
       <c r="R2" t="n">
-        <v>6599913</v>
+        <v>6599890</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hördes i flykt 3 gånger, sedan syntes den flyga här. Såg ett stort hålhack i närheten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,49 +788,45 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Jesper Granback, Anna Meijerhöffer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128754036</v>
+        <v>128752933</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348109</v>
+        <v>347987</v>
       </c>
       <c r="R3" t="n">
-        <v>6599890</v>
+        <v>6599913</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hördes i flykt 3 gånger, sedan syntes den flyga här. Såg ett stort hålhack i närheten.</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jesper Granback, Anna Meijerhöffer</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
